--- a/output/yearly_total_coral_cover_iteration_6_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_6_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.246325210822407</v>
+        <v>1.251656100856467</v>
       </c>
       <c r="C3" t="n">
-        <v>4.673145470462994</v>
+        <v>4.716931418072401</v>
       </c>
       <c r="D3" t="n">
-        <v>6.108596298129495</v>
+        <v>6.046363311157289</v>
       </c>
       <c r="E3" t="n">
-        <v>12.02806697941489</v>
+        <v>12.01495083008616</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.356296956359887</v>
+        <v>1.376385761999384</v>
       </c>
       <c r="C4" t="n">
-        <v>5.232776677728467</v>
+        <v>5.376594848349133</v>
       </c>
       <c r="D4" t="n">
-        <v>6.324285624507067</v>
+        <v>6.213269858535615</v>
       </c>
       <c r="E4" t="n">
-        <v>12.91335925859542</v>
+        <v>12.96625046888413</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.507985483291122</v>
+        <v>1.545775309768554</v>
       </c>
       <c r="C5" t="n">
-        <v>5.929533350193697</v>
+        <v>6.269745849825063</v>
       </c>
       <c r="D5" t="n">
-        <v>6.586965205150495</v>
+        <v>6.525889109914338</v>
       </c>
       <c r="E5" t="n">
-        <v>14.02448403863531</v>
+        <v>14.34141026950796</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.678453869535435</v>
+        <v>1.736041861495115</v>
       </c>
       <c r="C6" t="n">
-        <v>6.750288438532574</v>
+        <v>7.346439756636742</v>
       </c>
       <c r="D6" t="n">
-        <v>6.920191050180275</v>
+        <v>6.885045177548442</v>
       </c>
       <c r="E6" t="n">
-        <v>15.34893335824828</v>
+        <v>15.9675267956803</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1.872815750813925</v>
+        <v>1.93979783562372</v>
       </c>
       <c r="C7" t="n">
-        <v>7.69330697695121</v>
+        <v>8.571655265143093</v>
       </c>
       <c r="D7" t="n">
-        <v>7.236115241537476</v>
+        <v>7.312715277762295</v>
       </c>
       <c r="E7" t="n">
-        <v>16.80223796930261</v>
+        <v>17.82416837852911</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.12553155553125</v>
+        <v>1.173788634599355</v>
       </c>
       <c r="C8" t="n">
-        <v>5.246087541243076</v>
+        <v>6.120873745120035</v>
       </c>
       <c r="D8" t="n">
-        <v>5.43646253969596</v>
+        <v>5.510119910835125</v>
       </c>
       <c r="E8" t="n">
-        <v>11.80808163647029</v>
+        <v>12.80478229055452</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.417259458620207</v>
+        <v>1.459630865784092</v>
       </c>
       <c r="C9" t="n">
-        <v>6.380554592177089</v>
+        <v>7.528058168311228</v>
       </c>
       <c r="D9" t="n">
-        <v>5.867913441956508</v>
+        <v>5.993371758541723</v>
       </c>
       <c r="E9" t="n">
-        <v>13.6657274927538</v>
+        <v>14.98106079263704</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.728760745841345</v>
+        <v>1.757348774158712</v>
       </c>
       <c r="C10" t="n">
-        <v>7.665464289206751</v>
+        <v>9.114721005119025</v>
       </c>
       <c r="D10" t="n">
-        <v>6.277541471313305</v>
+        <v>6.516483577905759</v>
       </c>
       <c r="E10" t="n">
-        <v>15.6717665063614</v>
+        <v>17.3885533571835</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.039798721894165</v>
+        <v>2.038346623681716</v>
       </c>
       <c r="C11" t="n">
-        <v>9.057401569783503</v>
+        <v>10.88089065719589</v>
       </c>
       <c r="D11" t="n">
-        <v>6.712441881700733</v>
+        <v>7.02501627767888</v>
       </c>
       <c r="E11" t="n">
-        <v>17.8096421733784</v>
+        <v>19.94425355855649</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.375221006134187</v>
+        <v>2.310057130582497</v>
       </c>
       <c r="C12" t="n">
-        <v>10.54353300564365</v>
+        <v>12.77955611647578</v>
       </c>
       <c r="D12" t="n">
-        <v>7.200808012546179</v>
+        <v>7.506766167791334</v>
       </c>
       <c r="E12" t="n">
-        <v>20.11956202432402</v>
+        <v>22.59637941484961</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.709440731838575</v>
+        <v>2.553115997123796</v>
       </c>
       <c r="C13" t="n">
-        <v>12.0800161211733</v>
+        <v>14.7089565354758</v>
       </c>
       <c r="D13" t="n">
-        <v>7.652770029130447</v>
+        <v>7.954164814602121</v>
       </c>
       <c r="E13" t="n">
-        <v>22.44222688214232</v>
+        <v>25.21623734720172</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.565750143595068</v>
+        <v>1.461920506393925</v>
       </c>
       <c r="C14" t="n">
-        <v>8.568772502482501</v>
+        <v>10.39907419994096</v>
       </c>
       <c r="D14" t="n">
-        <v>5.834487336430624</v>
+        <v>6.060740912351345</v>
       </c>
       <c r="E14" t="n">
-        <v>15.96900998250819</v>
+        <v>17.92173561868623</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.618852876917778</v>
+        <v>1.46981375793607</v>
       </c>
       <c r="C15" t="n">
-        <v>9.166097258177388</v>
+        <v>11.34572442376094</v>
       </c>
       <c r="D15" t="n">
-        <v>5.830933409741251</v>
+        <v>6.063362178721682</v>
       </c>
       <c r="E15" t="n">
-        <v>16.61588354483641</v>
+        <v>18.8789003604187</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.904178212203029</v>
+        <v>1.66746902323208</v>
       </c>
       <c r="C16" t="n">
-        <v>10.77102895264895</v>
+        <v>13.4284432734583</v>
       </c>
       <c r="D16" t="n">
-        <v>6.3030460632365</v>
+        <v>6.490491152408343</v>
       </c>
       <c r="E16" t="n">
-        <v>18.97825322808847</v>
+        <v>21.58640344909872</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.551190825141088</v>
+        <v>1.313872952593506</v>
       </c>
       <c r="C17" t="n">
-        <v>9.850768107119114</v>
+        <v>12.30554970177192</v>
       </c>
       <c r="D17" t="n">
-        <v>5.859914601970617</v>
+        <v>5.992499629429148</v>
       </c>
       <c r="E17" t="n">
-        <v>17.26187353423082</v>
+        <v>19.61192228379458</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.798659968950582</v>
+        <v>1.471806705775691</v>
       </c>
       <c r="C18" t="n">
-        <v>11.45722151053225</v>
+        <v>14.38084653882517</v>
       </c>
       <c r="D18" t="n">
-        <v>6.276784312147897</v>
+        <v>6.379111875361542</v>
       </c>
       <c r="E18" t="n">
-        <v>19.53266579163073</v>
+        <v>22.2317651199624</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.830232975119159</v>
+        <v>1.450659860226214</v>
       </c>
       <c r="C19" t="n">
-        <v>12.206393183643</v>
+        <v>15.36885779342508</v>
       </c>
       <c r="D19" t="n">
-        <v>6.369323850750202</v>
+        <v>6.43773203078212</v>
       </c>
       <c r="E19" t="n">
-        <v>20.40595000951236</v>
+        <v>23.25724968443341</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.058715118328519</v>
+        <v>1.588595412672891</v>
       </c>
       <c r="C20" t="n">
-        <v>13.99671811458452</v>
+        <v>17.53631128747597</v>
       </c>
       <c r="D20" t="n">
-        <v>6.775855757601763</v>
+        <v>6.81247494697017</v>
       </c>
       <c r="E20" t="n">
-        <v>22.8312889905148</v>
+        <v>25.93738164711903</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.236845027718302</v>
+        <v>0.9308048158734434</v>
       </c>
       <c r="C21" t="n">
-        <v>10.28439625060789</v>
+        <v>12.77781943489985</v>
       </c>
       <c r="D21" t="n">
-        <v>5.641878254334443</v>
+        <v>5.685359860155534</v>
       </c>
       <c r="E21" t="n">
-        <v>17.16311953266063</v>
+        <v>19.39398411092883</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_6_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_6_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.251656100856467</v>
+        <v>1.283268376933214</v>
       </c>
       <c r="C3" t="n">
-        <v>4.716931418072401</v>
+        <v>4.601978579382142</v>
       </c>
       <c r="D3" t="n">
-        <v>6.046363311157289</v>
+        <v>6.064849620428257</v>
       </c>
       <c r="E3" t="n">
-        <v>12.01495083008616</v>
+        <v>11.95009657674361</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.376385761999384</v>
+        <v>1.450165416635274</v>
       </c>
       <c r="C4" t="n">
-        <v>5.376594848349133</v>
+        <v>5.045058023783426</v>
       </c>
       <c r="D4" t="n">
-        <v>6.213269858535615</v>
+        <v>6.375720960820721</v>
       </c>
       <c r="E4" t="n">
-        <v>12.96625046888413</v>
+        <v>12.87094440123942</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.545775309768554</v>
+        <v>1.673374462689389</v>
       </c>
       <c r="C5" t="n">
-        <v>6.269745849825063</v>
+        <v>5.588437826210902</v>
       </c>
       <c r="D5" t="n">
-        <v>6.525889109914338</v>
+        <v>6.635586276958467</v>
       </c>
       <c r="E5" t="n">
-        <v>14.34141026950796</v>
+        <v>13.89739856585876</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.736041861495115</v>
+        <v>1.919857000686977</v>
       </c>
       <c r="C6" t="n">
-        <v>7.346439756636742</v>
+        <v>6.244847789480815</v>
       </c>
       <c r="D6" t="n">
-        <v>6.885045177548442</v>
+        <v>6.958199768996479</v>
       </c>
       <c r="E6" t="n">
-        <v>15.9675267956803</v>
+        <v>15.12290455916427</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1.93979783562372</v>
+        <v>2.194712824999665</v>
       </c>
       <c r="C7" t="n">
-        <v>8.571655265143093</v>
+        <v>7.004535621559872</v>
       </c>
       <c r="D7" t="n">
-        <v>7.312715277762295</v>
+        <v>7.338706630223182</v>
       </c>
       <c r="E7" t="n">
-        <v>17.82416837852911</v>
+        <v>16.53795507678272</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.173788634599355</v>
+        <v>1.39633667226436</v>
       </c>
       <c r="C8" t="n">
-        <v>6.120873745120035</v>
+        <v>4.630512956286157</v>
       </c>
       <c r="D8" t="n">
-        <v>5.510119910835125</v>
+        <v>5.540993999000892</v>
       </c>
       <c r="E8" t="n">
-        <v>12.80478229055452</v>
+        <v>11.56784362755141</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.459630865784092</v>
+        <v>1.779351489161307</v>
       </c>
       <c r="C9" t="n">
-        <v>7.528058168311228</v>
+        <v>5.583024160081471</v>
       </c>
       <c r="D9" t="n">
-        <v>5.993371758541723</v>
+        <v>6.087887194548241</v>
       </c>
       <c r="E9" t="n">
-        <v>14.98106079263704</v>
+        <v>13.45026284379102</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.757348774158712</v>
+        <v>2.183373755743637</v>
       </c>
       <c r="C10" t="n">
-        <v>9.114721005119025</v>
+        <v>6.675380577650682</v>
       </c>
       <c r="D10" t="n">
-        <v>6.516483577905759</v>
+        <v>6.580798437651866</v>
       </c>
       <c r="E10" t="n">
-        <v>17.3885533571835</v>
+        <v>15.43955277104618</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.038346623681716</v>
+        <v>2.591380738989328</v>
       </c>
       <c r="C11" t="n">
-        <v>10.88089065719589</v>
+        <v>7.940432599340656</v>
       </c>
       <c r="D11" t="n">
-        <v>7.02501627767888</v>
+        <v>7.093176092616617</v>
       </c>
       <c r="E11" t="n">
-        <v>19.94425355855649</v>
+        <v>17.6249894309466</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.310057130582497</v>
+        <v>3.027910427779624</v>
       </c>
       <c r="C12" t="n">
-        <v>12.77955611647578</v>
+        <v>9.32488868813415</v>
       </c>
       <c r="D12" t="n">
-        <v>7.506766167791334</v>
+        <v>7.629929916469031</v>
       </c>
       <c r="E12" t="n">
-        <v>22.59637941484961</v>
+        <v>19.98272903238281</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.553115997123796</v>
+        <v>3.449312025194852</v>
       </c>
       <c r="C13" t="n">
-        <v>14.7089565354758</v>
+        <v>10.76524183779703</v>
       </c>
       <c r="D13" t="n">
-        <v>7.954164814602121</v>
+        <v>8.151022184121324</v>
       </c>
       <c r="E13" t="n">
-        <v>25.21623734720172</v>
+        <v>22.36557604711321</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.461920506393925</v>
+        <v>2.001489044647972</v>
       </c>
       <c r="C14" t="n">
-        <v>10.39907419994096</v>
+        <v>7.655334803497184</v>
       </c>
       <c r="D14" t="n">
-        <v>6.060740912351345</v>
+        <v>6.220441811401173</v>
       </c>
       <c r="E14" t="n">
-        <v>17.92173561868623</v>
+        <v>15.87726565954633</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.46981375793607</v>
+        <v>2.073028999856438</v>
       </c>
       <c r="C15" t="n">
-        <v>11.34572442376094</v>
+        <v>8.274081294098737</v>
       </c>
       <c r="D15" t="n">
-        <v>6.063362178721682</v>
+        <v>6.246556300334138</v>
       </c>
       <c r="E15" t="n">
-        <v>18.8789003604187</v>
+        <v>16.59366659428931</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.66746902323208</v>
+        <v>2.438906734275139</v>
       </c>
       <c r="C16" t="n">
-        <v>13.4284432734583</v>
+        <v>9.774879009580834</v>
       </c>
       <c r="D16" t="n">
-        <v>6.490491152408343</v>
+        <v>6.730067044675693</v>
       </c>
       <c r="E16" t="n">
-        <v>21.58640344909872</v>
+        <v>18.94385278853166</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.313872952593506</v>
+        <v>1.972939821408475</v>
       </c>
       <c r="C17" t="n">
-        <v>12.30554970177192</v>
+        <v>9.055876443421598</v>
       </c>
       <c r="D17" t="n">
-        <v>5.992499629429148</v>
+        <v>6.269283759687451</v>
       </c>
       <c r="E17" t="n">
-        <v>19.61192228379458</v>
+        <v>17.29810002451752</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.471806705775691</v>
+        <v>2.28004032077392</v>
       </c>
       <c r="C18" t="n">
-        <v>14.38084653882517</v>
+        <v>10.5467585070908</v>
       </c>
       <c r="D18" t="n">
-        <v>6.379111875361542</v>
+        <v>6.697060686858913</v>
       </c>
       <c r="E18" t="n">
-        <v>22.2317651199624</v>
+        <v>19.52385951472364</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.450659860226214</v>
+        <v>2.314833459412426</v>
       </c>
       <c r="C19" t="n">
-        <v>15.36885779342508</v>
+        <v>11.25882011698102</v>
       </c>
       <c r="D19" t="n">
-        <v>6.43773203078212</v>
+        <v>6.797984350855487</v>
       </c>
       <c r="E19" t="n">
-        <v>23.25724968443341</v>
+        <v>20.37163792724893</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.588595412672891</v>
+        <v>2.617849888328205</v>
       </c>
       <c r="C20" t="n">
-        <v>17.53631128747597</v>
+        <v>12.91839588867095</v>
       </c>
       <c r="D20" t="n">
-        <v>6.81247494697017</v>
+        <v>7.2897614108668</v>
       </c>
       <c r="E20" t="n">
-        <v>25.93738164711903</v>
+        <v>22.82600718786596</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0.9308048158734434</v>
+        <v>1.581585734064569</v>
       </c>
       <c r="C21" t="n">
-        <v>12.77781943489985</v>
+        <v>9.464823449625607</v>
       </c>
       <c r="D21" t="n">
-        <v>5.685359860155534</v>
+        <v>6.084165412574674</v>
       </c>
       <c r="E21" t="n">
-        <v>19.39398411092883</v>
+        <v>17.13057459626485</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_6_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_6_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.283268376933214</v>
+        <v>2.606500406750641</v>
       </c>
       <c r="C3" t="n">
-        <v>4.601978579382142</v>
+        <v>7.742982407888844</v>
       </c>
       <c r="D3" t="n">
-        <v>6.064849620428257</v>
+        <v>8.155179634694827</v>
       </c>
       <c r="E3" t="n">
-        <v>11.95009657674361</v>
+        <v>18.50466244933431</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.450165416635274</v>
+        <v>1.107420624667875</v>
       </c>
       <c r="C4" t="n">
-        <v>5.045058023783426</v>
+        <v>4.600201573795953</v>
       </c>
       <c r="D4" t="n">
-        <v>6.375720960820721</v>
+        <v>5.697700388584611</v>
       </c>
       <c r="E4" t="n">
-        <v>12.87094440123942</v>
+        <v>11.40532258704844</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.673374462689389</v>
+        <v>1.236250099703696</v>
       </c>
       <c r="C5" t="n">
-        <v>5.588437826210902</v>
+        <v>5.376245567538383</v>
       </c>
       <c r="D5" t="n">
-        <v>6.635586276958467</v>
+        <v>5.922826035661518</v>
       </c>
       <c r="E5" t="n">
-        <v>13.89739856585876</v>
+        <v>12.5353217029036</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.919857000686977</v>
+        <v>1.38887258265117</v>
       </c>
       <c r="C6" t="n">
-        <v>6.244847789480815</v>
+        <v>6.361698047003696</v>
       </c>
       <c r="D6" t="n">
-        <v>6.958199768996479</v>
+        <v>6.225789717718678</v>
       </c>
       <c r="E6" t="n">
-        <v>15.12290455916427</v>
+        <v>13.97636034737354</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.194712824999665</v>
+        <v>1.544753188969433</v>
       </c>
       <c r="C7" t="n">
-        <v>7.004535621559872</v>
+        <v>7.511836288224811</v>
       </c>
       <c r="D7" t="n">
-        <v>7.338706630223182</v>
+        <v>6.547452190924309</v>
       </c>
       <c r="E7" t="n">
-        <v>16.53795507678272</v>
+        <v>15.60404166811855</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.39633667226436</v>
+        <v>1.711251971633927</v>
       </c>
       <c r="C8" t="n">
-        <v>4.630512956286157</v>
+        <v>8.838240489032936</v>
       </c>
       <c r="D8" t="n">
-        <v>5.540993999000892</v>
+        <v>6.896467622005114</v>
       </c>
       <c r="E8" t="n">
-        <v>11.56784362755141</v>
+        <v>17.44596008267198</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.779351489161307</v>
+        <v>1.853477194281608</v>
       </c>
       <c r="C9" t="n">
-        <v>5.583024160081471</v>
+        <v>10.3590246309206</v>
       </c>
       <c r="D9" t="n">
-        <v>6.087887194548241</v>
+        <v>7.204631033993914</v>
       </c>
       <c r="E9" t="n">
-        <v>13.45026284379102</v>
+        <v>19.41713285919612</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.183373755743637</v>
+        <v>1.134978885925652</v>
       </c>
       <c r="C10" t="n">
-        <v>6.675380577650682</v>
+        <v>7.57652009780025</v>
       </c>
       <c r="D10" t="n">
-        <v>6.580798437651866</v>
+        <v>5.665175127356219</v>
       </c>
       <c r="E10" t="n">
-        <v>15.43955277104618</v>
+        <v>14.37667411108212</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.591380738989328</v>
+        <v>1.072451374642173</v>
       </c>
       <c r="C11" t="n">
-        <v>7.940432599340656</v>
+        <v>8.298654439136033</v>
       </c>
       <c r="D11" t="n">
-        <v>7.093176092616617</v>
+        <v>5.462503131291507</v>
       </c>
       <c r="E11" t="n">
-        <v>17.6249894309466</v>
+        <v>14.83360894506971</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.027910427779624</v>
+        <v>1.160573048575367</v>
       </c>
       <c r="C12" t="n">
-        <v>9.32488868813415</v>
+        <v>10.02882768823836</v>
       </c>
       <c r="D12" t="n">
-        <v>7.629929916469031</v>
+        <v>5.72901818056339</v>
       </c>
       <c r="E12" t="n">
-        <v>19.98272903238281</v>
+        <v>16.91841891737711</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.449312025194852</v>
+        <v>0.9140954699471627</v>
       </c>
       <c r="C13" t="n">
-        <v>10.76524183779703</v>
+        <v>9.69884264988692</v>
       </c>
       <c r="D13" t="n">
-        <v>8.151022184121324</v>
+        <v>5.143268230301572</v>
       </c>
       <c r="E13" t="n">
-        <v>22.36557604711321</v>
+        <v>15.75620635013566</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.001489044647972</v>
+        <v>0.9843493356630646</v>
       </c>
       <c r="C14" t="n">
-        <v>7.655334803497184</v>
+        <v>11.56286738098625</v>
       </c>
       <c r="D14" t="n">
-        <v>6.220441811401173</v>
+        <v>5.430419616316722</v>
       </c>
       <c r="E14" t="n">
-        <v>15.87726565954633</v>
+        <v>17.97763633296604</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2.073028999856438</v>
+        <v>0.9474748918915542</v>
       </c>
       <c r="C15" t="n">
-        <v>8.274081294098737</v>
+        <v>12.66519333826866</v>
       </c>
       <c r="D15" t="n">
-        <v>6.246556300334138</v>
+        <v>5.412070751724348</v>
       </c>
       <c r="E15" t="n">
-        <v>16.59366659428931</v>
+        <v>19.02473898188456</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.438906734275139</v>
+        <v>1.030952899183661</v>
       </c>
       <c r="C16" t="n">
-        <v>9.774879009580834</v>
+        <v>14.86190291390611</v>
       </c>
       <c r="D16" t="n">
-        <v>6.730067044675693</v>
+        <v>5.721488175671817</v>
       </c>
       <c r="E16" t="n">
-        <v>18.94385278853166</v>
+        <v>21.61434398876159</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.972939821408475</v>
+        <v>0.6120117013504192</v>
       </c>
       <c r="C17" t="n">
-        <v>9.055876443421598</v>
+        <v>11.14129509930563</v>
       </c>
       <c r="D17" t="n">
-        <v>6.269283759687451</v>
+        <v>4.703405988890832</v>
       </c>
       <c r="E17" t="n">
-        <v>17.29810002451752</v>
+        <v>16.45671278954688</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2.28004032077392</v>
+        <v>0.480486961412474</v>
       </c>
       <c r="C18" t="n">
-        <v>10.5467585070908</v>
+        <v>10.15522770516013</v>
       </c>
       <c r="D18" t="n">
-        <v>6.697060686858913</v>
+        <v>4.195341734466064</v>
       </c>
       <c r="E18" t="n">
-        <v>19.52385951472364</v>
+        <v>14.83105640103867</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2.314833459412426</v>
+        <v>0.5581922922036091</v>
       </c>
       <c r="C19" t="n">
-        <v>11.25882011698102</v>
+        <v>12.63101870068382</v>
       </c>
       <c r="D19" t="n">
-        <v>6.797984350855487</v>
+        <v>4.55562350697056</v>
       </c>
       <c r="E19" t="n">
-        <v>20.37163792724893</v>
+        <v>17.74483449985799</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.617849888328205</v>
+        <v>0.6269833538401831</v>
       </c>
       <c r="C20" t="n">
-        <v>12.91839588867095</v>
+        <v>15.21311333762336</v>
       </c>
       <c r="D20" t="n">
-        <v>7.2897614108668</v>
+        <v>4.959278893048678</v>
       </c>
       <c r="E20" t="n">
-        <v>22.82600718786596</v>
+        <v>20.79937558451222</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.581585734064569</v>
+        <v>0.6876553619626359</v>
       </c>
       <c r="C21" t="n">
-        <v>9.464823449625607</v>
+        <v>17.71151398277586</v>
       </c>
       <c r="D21" t="n">
-        <v>6.084165412574674</v>
+        <v>5.29930721041456</v>
       </c>
       <c r="E21" t="n">
-        <v>17.13057459626485</v>
+        <v>23.69847655515305</v>
       </c>
     </row>
   </sheetData>
